--- a/templates/appendix3_template.xlsx
+++ b/templates/appendix3_template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Приложение 3" sheetId="1" r:id="Rb31fe95ecd50481f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Приложение 3" sheetId="1" r:id="Rab131307f25543f1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -28,6 +28,11 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FF17324D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -56,7 +61,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -99,6 +104,22 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -303,143 +324,203 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="44" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="60" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="23" t="str">
         <x:v>Приложение 3 — результаты правового мониторинга</x:v>
       </x:c>
+      <x:c r="B1" s="24"/>
+      <x:c r="C1" s="24"/>
+      <x:c r="D1" s="24"/>
+      <x:c r="E1" s="24"/>
+      <x:c r="F1" s="24"/>
+      <x:c r="G1" s="24"/>
+      <x:c r="H1" s="24"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="24"/>
+      <x:c r="B2" s="24"/>
+      <x:c r="C2" s="24"/>
+      <x:c r="D2" s="24"/>
+      <x:c r="E2" s="24"/>
+      <x:c r="F2" s="24"/>
+      <x:c r="G2" s="24"/>
+      <x:c r="H2" s="24"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
+      <x:c r="A3" s="24" t="str">
         <x:v>Наименование, номер и дата принятия документа, в отношении которого проведён правовой мониторинг:</x:v>
       </x:c>
+      <x:c r="B3" s="24"/>
+      <x:c r="C3" s="24"/>
+      <x:c r="D3" s="24"/>
+      <x:c r="E3" s="24"/>
+      <x:c r="F3" s="24"/>
+      <x:c r="G3" s="24"/>
+      <x:c r="H3" s="24"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="24"/>
+      <x:c r="B4" s="24"/>
+      <x:c r="C4" s="24"/>
+      <x:c r="D4" s="24"/>
+      <x:c r="E4" s="24"/>
+      <x:c r="F4" s="24"/>
+      <x:c r="G4" s="24"/>
+      <x:c r="H4" s="24"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="14" t="str">
+      <x:c r="A5" s="25" t="str">
         <x:v>№ п/п</x:v>
       </x:c>
-      <x:c r="B5" s="14" t="str">
+      <x:c r="B5" s="25" t="str">
         <x:v>Виды недостатков норм поведения</x:v>
       </x:c>
-      <x:c r="C5" s="14" t="str">
-        <x:v>Структурные элементы документа (страница, абзац, подпункт, пункт, статья, часть и пр.)</x:v>
-      </x:c>
-      <x:c r="D5" s="14" t="str">
+      <x:c r="C5" s="25" t="str">
+        <x:v>Наименование ВНД</x:v>
+      </x:c>
+      <x:c r="D5" s="25" t="str">
+        <x:v>Номер и дата принятия ВНД</x:v>
+      </x:c>
+      <x:c r="E5" s="25" t="str">
+        <x:v>Структурные элементы документа (абзац, подпункт, пункт, статья, часть и др.)</x:v>
+      </x:c>
+      <x:c r="F5" s="25" t="str">
         <x:v>Номер и наименование акта, которому не соответствует норма поведения документа</x:v>
       </x:c>
-      <x:c r="E5" s="14" t="str">
-        <x:v>Предпринимаемые меры по устранению выявленных недостатков и противоречий</x:v>
-      </x:c>
-      <x:c r="F5" s="14" t="str">
-        <x:v>Сведения об актуализации документа</x:v>
+      <x:c r="G5" s="26" t="str">
+        <x:v>Предпринимаемые меры по устранению выявленных недостатков и противоречий (наименование проекта документа, стадия разработки либо согласования)</x:v>
+      </x:c>
+      <x:c r="H5" s="26" t="str">
+        <x:v>Сведения об актуализации документа (наименование документа, дата утверждения и пр.)</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="20" t="n">
+      <x:c r="A6" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="20" t="str">
+      <x:c r="B6" s="24" t="str">
         <x:v>Неэффективно реализуемые нормы</x:v>
       </x:c>
-      <x:c r="C6" s="20" t="str"/>
-      <x:c r="D6" s="20" t="str"/>
-      <x:c r="E6" s="20" t="str"/>
-      <x:c r="F6" s="20" t="str"/>
+      <x:c r="C6" s="24" t="str"/>
+      <x:c r="D6" s="24" t="str"/>
+      <x:c r="E6" s="24" t="str"/>
+      <x:c r="F6" s="24" t="str"/>
+      <x:c r="G6" s="24" t="str"/>
+      <x:c r="H6" s="24" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="20" t="n">
+      <x:c r="A7" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="20" t="str">
+      <x:c r="B7" s="24" t="str">
         <x:v>Противоречащие нормы</x:v>
       </x:c>
-      <x:c r="C7" s="20" t="str"/>
-      <x:c r="D7" s="20" t="str"/>
-      <x:c r="E7" s="20" t="str"/>
-      <x:c r="F7" s="20" t="str"/>
+      <x:c r="C7" s="24" t="str"/>
+      <x:c r="D7" s="24" t="str"/>
+      <x:c r="E7" s="24" t="str"/>
+      <x:c r="F7" s="24" t="str"/>
+      <x:c r="G7" s="24" t="str"/>
+      <x:c r="H7" s="24" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="20" t="n">
+      <x:c r="A8" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" s="20" t="str">
+      <x:c r="B8" s="24" t="str">
         <x:v>Устаревшие нормы</x:v>
       </x:c>
-      <x:c r="C8" s="20" t="str"/>
-      <x:c r="D8" s="20" t="str"/>
-      <x:c r="E8" s="20" t="str"/>
-      <x:c r="F8" s="20" t="str"/>
+      <x:c r="C8" s="24" t="str"/>
+      <x:c r="D8" s="24" t="str"/>
+      <x:c r="E8" s="24" t="str"/>
+      <x:c r="F8" s="24" t="str"/>
+      <x:c r="G8" s="24" t="str"/>
+      <x:c r="H8" s="24" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="20" t="n">
+      <x:c r="A9" s="24" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="20" t="str">
+      <x:c r="B9" s="24" t="str">
         <x:v>Коррупциогенные нормы</x:v>
       </x:c>
-      <x:c r="C9" s="20" t="str"/>
-      <x:c r="D9" s="20" t="str"/>
-      <x:c r="E9" s="20" t="str"/>
-      <x:c r="F9" s="20" t="str"/>
+      <x:c r="C9" s="24" t="str"/>
+      <x:c r="D9" s="24" t="str"/>
+      <x:c r="E9" s="24" t="str"/>
+      <x:c r="F9" s="24" t="str"/>
+      <x:c r="G9" s="24" t="str"/>
+      <x:c r="H9" s="24" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="20" t="n">
+      <x:c r="A10" s="24" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B10" s="20" t="str">
+      <x:c r="B10" s="24" t="str">
         <x:v>Дублирующие нормы</x:v>
       </x:c>
-      <x:c r="C10" s="20" t="str"/>
-      <x:c r="D10" s="20" t="str"/>
-      <x:c r="E10" s="20" t="str"/>
-      <x:c r="F10" s="20" t="str"/>
+      <x:c r="C10" s="24" t="str"/>
+      <x:c r="D10" s="24" t="str"/>
+      <x:c r="E10" s="24" t="str"/>
+      <x:c r="F10" s="24" t="str"/>
+      <x:c r="G10" s="24" t="str"/>
+      <x:c r="H10" s="24" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="20" t="n">
+      <x:c r="A11" s="24" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B11" s="20" t="str">
+      <x:c r="B11" s="24" t="str">
         <x:v>Пробелы норм права</x:v>
       </x:c>
-      <x:c r="C11" s="20" t="str"/>
-      <x:c r="D11" s="20" t="str"/>
-      <x:c r="E11" s="20" t="str"/>
-      <x:c r="F11" s="20" t="str"/>
+      <x:c r="C11" s="24" t="str"/>
+      <x:c r="D11" s="24" t="str"/>
+      <x:c r="E11" s="24" t="str"/>
+      <x:c r="F11" s="24" t="str"/>
+      <x:c r="G11" s="24" t="str"/>
+      <x:c r="H11" s="24" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="20" t="n">
+      <x:c r="A12" s="24" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B12" s="20" t="str">
+      <x:c r="B12" s="24" t="str">
         <x:v>Наличие излишних бланкетных и отсылочных норм</x:v>
       </x:c>
-      <x:c r="C12" s="20" t="str"/>
-      <x:c r="D12" s="20" t="str"/>
-      <x:c r="E12" s="20" t="str"/>
-      <x:c r="F12" s="20" t="str"/>
+      <x:c r="C12" s="24" t="str"/>
+      <x:c r="D12" s="24" t="str"/>
+      <x:c r="E12" s="24" t="str"/>
+      <x:c r="F12" s="24" t="str"/>
+      <x:c r="G12" s="24" t="str"/>
+      <x:c r="H12" s="24" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="20" t="n">
+      <x:c r="A13" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B13" s="20" t="str">
+      <x:c r="B13" s="24" t="str">
         <x:v>Иное</x:v>
       </x:c>
-      <x:c r="C13" s="20" t="str"/>
-      <x:c r="D13" s="20" t="str"/>
-      <x:c r="E13" s="20" t="str"/>
-      <x:c r="F13" s="20" t="str"/>
+      <x:c r="C13" s="24" t="str"/>
+      <x:c r="D13" s="24" t="str"/>
+      <x:c r="E13" s="24" t="str"/>
+      <x:c r="F13" s="24" t="str"/>
+      <x:c r="G13" s="24" t="str"/>
+      <x:c r="H13" s="24" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A3:F3"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A3:H3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
